--- a/Templates/DsHoaDon_Template.xlsx
+++ b/Templates/DsHoaDon_Template.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Quay27\Quay27-Be\Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC24004A-65ED-4898-AE90-43434F4BCA26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DanhSachHoaDon_KV22032026-21195" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="DanhSachHoaDon_KV22032026-21195" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -22,34 +27,32 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t xml:space="preserve">Mã hóa đơn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thời gian</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Khách hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Người tạo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tổng tiền hàng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Số lượng</t>
+    <t>Mã hóa đơn</t>
+  </si>
+  <si>
+    <t>Thời gian</t>
+  </si>
+  <si>
+    <t>Khách hàng</t>
+  </si>
+  <si>
+    <t>Người tạo</t>
+  </si>
+  <si>
+    <t>Số lượng</t>
+  </si>
+  <si>
+    <t>NV Soạn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="#,##0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,32 +61,15 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="2">
@@ -95,7 +81,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -103,131 +89,83 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="InvoiceTable" displayName="InvoiceTable" ref="A1:F16" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:F16"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="InvoiceTable" displayName="InvoiceTable" ref="A1:F16" totalsRowShown="0">
+  <autoFilter ref="A1:F16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Mã hóa đơn"/>
-    <tableColumn id="2" name="Thời gian"/>
-    <tableColumn id="3" name="Khách hàng"/>
-    <tableColumn id="4" name="Người tạo"/>
-    <tableColumn id="5" name="Tổng tiền hàng"/>
-    <tableColumn id="6" name="Số lượng"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Mã hóa đơn"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Thời gian"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Khách hàng"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Người tạo"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="NV Soạn"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Số lượng"/>
   </tableColumns>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
     <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -235,12 +173,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -269,7 +207,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -290,7 +228,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -341,7 +279,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -359,30 +297,29 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="16.43"/>
+    <col min="1" max="1" width="14.140625" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="12.42578125" customWidth="1"/>
+    <col min="5" max="6" width="16.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -396,97 +333,92 @@
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" s="1"/>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="F5" s="4"/>
       <c r="G5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
       <c r="F8" s="4"/>
       <c r="G8" s="4"/>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="F11" s="4"/>
       <c r="G11" s="4"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
       <c r="F13" s="4"/>
       <c r="G13" s="4"/>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <tableParts>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
